--- a/26/赵鑫_产研部_2026年中自评表.xlsx
+++ b/26/赵鑫_产研部_2026年中自评表.xlsx
@@ -209,7 +209,8 @@
   <si>
     <t xml:space="preserve">一、OKR1：支撑业务增长，推进目标落地
    上半年参与95个需求，覆盖机构接入、CA签章、账务核心、运营支持等场景；
-   14家机构产品上线，11家机构CA签章对接，保障合规放款；
+   新增14 家机构产品上线（12家我方标准文档+2家机构文档）；
+   11家机构CA签章对接，保障合规放款；
    数据治理一期收尾，异常借据从3.4万降至340笔；
    数据治理二期合规补充，45个产品67个问题全部完成沟通和确认；
 二、OKR2：研发效率提升

--- a/26/赵鑫_产研部_2026年中自评表.xlsx
+++ b/26/赵鑫_产研部_2026年中自评表.xlsx
@@ -209,7 +209,7 @@
   <si>
     <t xml:space="preserve">一、OKR1：支撑业务增长，推进目标落地
    上半年参与95个需求，覆盖机构接入、CA签章、账务核心、运营支持等场景；
-   新增14 家机构产品上线（12家我方标准文档+2家机构文档）；
+   新增13 家机构产品上线（11家我方标准文档+2家机构文档）；
    11家机构CA签章对接，保障合规放款；
    数据治理一期收尾，异常借据从3.4万降至340笔；
    数据治理二期合规补充，45个产品67个问题全部完成沟通和确认；
